--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mood/current_mood_vs_mobile_navigation.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mood/current_mood_vs_mobile_navigation.xlsx
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
         <v>5</v>
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -538,13 +538,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>5</v>
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
